--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>92.94348082340844</v>
+        <v>15.10331563380387</v>
       </c>
       <c r="D2" t="n">
-        <v>50.52531039961816</v>
+        <v>8.210362939937951</v>
       </c>
       <c r="E2" t="n">
-        <v>19.93497770717715</v>
+        <v>3.239433877416288</v>
       </c>
       <c r="F2" t="n">
-        <v>18.68746705949766</v>
+        <v>3.03671339716837</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.07352540905413</v>
+        <v>8.624447878971296</v>
       </c>
       <c r="D3" t="n">
-        <v>13.15037628062285</v>
+        <v>2.136936145601213</v>
       </c>
       <c r="E3" t="n">
-        <v>19.93497770717715</v>
+        <v>3.239433877416288</v>
       </c>
       <c r="F3" t="n">
-        <v>18.68746705949766</v>
+        <v>3.03671339716837</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
